--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20221.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -70,25 +70,10 @@
     <t>GIL</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
     <t>JOSE RAUL</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>JORGE IVAN</t>
   </si>
 </sst>
 </file>
@@ -486,10 +471,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>7</v>
@@ -498,7 +483,7 @@
         <v>23</v>
       </c>
       <c r="G2">
-        <v>74.19</v>
+        <v>76.67</v>
       </c>
       <c r="H2">
         <v>7.8</v>
@@ -551,10 +536,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2">
         <v>30</v>
@@ -613,10 +598,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>7</v>
@@ -625,7 +610,7 @@
         <v>23</v>
       </c>
       <c r="G2">
-        <v>74.19</v>
+        <v>76.67</v>
       </c>
       <c r="H2">
         <v>7.8</v>
@@ -638,7 +623,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -676,10 +661,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
         <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -688,52 +673,6 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920045</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920327</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20221.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
   <si>
     <t>Mat</t>
   </si>
@@ -65,15 +65,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>JOSE RAUL</t>
   </si>
 </sst>
 </file>
@@ -539,16 +530,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H2">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -604,16 +598,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>76.67</v>
+        <v>86.67</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -623,7 +617,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -653,29 +647,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920036</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20221.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -65,6 +65,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>JOSE RAUL</t>
   </si>
 </sst>
 </file>
@@ -598,16 +607,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>86.67</v>
+        <v>80</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -617,7 +626,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -647,6 +656,29 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920036</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20221.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -67,10 +67,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>GIL</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
   </si>
   <si>
     <t>JOSE RAUL</t>
@@ -539,16 +548,16 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>86.67</v>
       </c>
       <c r="H2">
         <v>7.8</v>
@@ -626,7 +635,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -658,16 +667,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920036</v>
+        <v>22330051920045</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -676,6 +685,29 @@
         <v>9</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920036</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
     </row>
